--- a/artfynd/A 52227-2024 artfynd.xlsx
+++ b/artfynd/A 52227-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85419996</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,8 +916,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85419998</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 52227-2024 artfynd.xlsx
+++ b/artfynd/A 52227-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,53 +680,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>85419996</v>
+        <v>136193396</v>
       </c>
       <c r="B2" t="n">
-        <v>57141</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hällesjö, Jmt</t>
+          <t>Vallsjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557469</v>
+        <v>557483</v>
       </c>
       <c r="R2" t="n">
-        <v>6975768</v>
+        <v>6975725</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,27 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-05-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>04:37</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-05-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>04:37</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Stöttes åt V. Kan inte varit samma tupp som stöttes åt N</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,24 +769,24 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85419996</t>
+          <t>https://artportalen.se/Sighting/136193396</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>85419998</v>
+        <v>85419996</v>
       </c>
       <c r="B3" t="n">
         <v>57141</v>
@@ -833,7 +817,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557552</v>
+        <v>557469</v>
       </c>
       <c r="R3" t="n">
-        <v>6975765</v>
+        <v>6975768</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>04:28</t>
+          <t>04:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +871,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>04:28</t>
+          <t>04:37</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Stöttes utom sikt, troligen höna</t>
+          <t>Stöttes åt V. Kan inte varit samma tupp som stöttes åt N</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,6 +901,128 @@
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85419996</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>85419998</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>557552</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6975765</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-05-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>04:28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-05-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>04:28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stöttes utom sikt, troligen höna</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/85419998</t>
         </is>
@@ -926,6 +1032,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52227-2024 artfynd.xlsx
+++ b/artfynd/A 52227-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193396</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52227-2024 artfynd.xlsx
+++ b/artfynd/A 52227-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193396</v>
       </c>
       <c r="B2" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52227-2024 artfynd.xlsx
+++ b/artfynd/A 52227-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193396</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52227-2024 artfynd.xlsx
+++ b/artfynd/A 52227-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193396</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
